--- a/Military_Combat_Force_ReportT.xlsx
+++ b/Military_Combat_Force_ReportT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\PowerBITables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A7453C2-9A46-4F82-8891-9E06B7358534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF18CE9C-8A38-42FA-BFE9-770639A87A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B3644927-FBA1-49E2-BE24-020467E64038}"/>
   </bookViews>
@@ -124,9 +124,6 @@
     <t>Allocated Equipment AssetClass</t>
   </si>
   <si>
-    <t>Strategic Command Sector</t>
-  </si>
-  <si>
     <t>Special Operations Hardware</t>
   </si>
   <si>
@@ -172,9 +169,6 @@
     <t>Orbital Telemetry Systems</t>
   </si>
   <si>
-    <t>Active Combat Unit Name</t>
-  </si>
-  <si>
     <t>3rd Infantry Division: 1st BCT</t>
   </si>
   <si>
@@ -251,6 +245,12 @@
   </si>
   <si>
     <t>Unit ID Code</t>
+  </si>
+  <si>
+    <t>Agency</t>
+  </si>
+  <si>
+    <t>Command Tier</t>
   </si>
 </sst>
 </file>
@@ -808,8 +808,8 @@
   <autoFilter ref="A1:G26" xr:uid="{DDFD3415-25DE-4EB8-B17F-AC298BEBBA37}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{E1AD40DB-35FA-42C2-905E-653B292F9DEB}" name="Unit ID Code"/>
-    <tableColumn id="2" xr3:uid="{0D253762-6745-44E6-80B4-94C0F44E127A}" name="Active Combat Unit Name"/>
-    <tableColumn id="3" xr3:uid="{1373A1BE-8B11-4281-97F1-4630D1E7613C}" name="Strategic Command Sector"/>
+    <tableColumn id="2" xr3:uid="{0D253762-6745-44E6-80B4-94C0F44E127A}" name="Agency"/>
+    <tableColumn id="3" xr3:uid="{1373A1BE-8B11-4281-97F1-4630D1E7613C}" name="Command Tier"/>
     <tableColumn id="4" xr3:uid="{453C3E0C-B54B-4184-B0F2-110656AE3141}" name="Allocated Equipment AssetClass"/>
     <tableColumn id="5" xr3:uid="{F86DD8E2-A7F9-4BD8-9BE0-1BDCEB5DF0FB}" name="Bulk Item Inventory Count" dataDxfId="1"/>
     <tableColumn id="6" xr3:uid="{DA309708-BCDD-48E8-9253-55D58080155D}" name="Lifetime Maintenance Run Hours" dataDxfId="0"/>
@@ -1150,13 +1150,13 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" t="s">
         <v>76</v>
-      </c>
-      <c r="B1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" t="s">
-        <v>34</v>
       </c>
       <c r="D1" t="s">
         <v>33</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E2" s="2">
         <v>5100</v>
@@ -1199,13 +1199,13 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2">
         <v>4950</v>
@@ -1222,13 +1222,13 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2">
         <v>4500</v>
@@ -1245,13 +1245,13 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2">
         <v>4200</v>
@@ -1268,13 +1268,13 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2">
         <v>2800</v>
@@ -1291,13 +1291,13 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2">
         <v>1920</v>
@@ -1314,13 +1314,13 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2">
         <v>1850</v>
@@ -1337,13 +1337,13 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E9" s="2">
         <v>1500</v>
@@ -1360,13 +1360,13 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2">
         <v>950</v>
@@ -1383,13 +1383,13 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C11" t="s">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E11" s="2">
         <v>310</v>
@@ -1406,13 +1406,13 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E12" s="2">
         <v>120</v>
@@ -1429,13 +1429,13 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E13" s="2">
         <v>6200</v>
@@ -1452,13 +1452,13 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E14" s="2">
         <v>5800</v>
@@ -1475,13 +1475,13 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E15" s="2">
         <v>4300</v>
@@ -1498,13 +1498,13 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16" s="2">
         <v>4120</v>
@@ -1521,13 +1521,13 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E17" s="2">
         <v>3200</v>
@@ -1544,13 +1544,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E18" s="2">
         <v>1400</v>
@@ -1567,13 +1567,13 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E19" s="2">
         <v>680</v>
@@ -1590,13 +1590,13 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E20" s="2">
         <v>85</v>
@@ -1613,13 +1613,13 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s">
         <v>23</v>
       </c>
       <c r="D21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E21" s="2">
         <v>3400</v>
@@ -1636,13 +1636,13 @@
         <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
         <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E22" s="2">
         <v>1200</v>
@@ -1659,13 +1659,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s">
         <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E23" s="2">
         <v>3900</v>
@@ -1682,13 +1682,13 @@
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s">
         <v>26</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E24" s="2">
         <v>3800</v>
@@ -1705,13 +1705,13 @@
         <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C25" t="s">
         <v>26</v>
       </c>
       <c r="D25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E25" s="2">
         <v>3100</v>
@@ -1728,13 +1728,13 @@
         <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s">
         <v>26</v>
       </c>
       <c r="D26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2">
         <v>240</v>
